--- a/experiments/results/resnet18/CIFAR-10/ReAct/adaptive/std/results.xlsx
+++ b/experiments/results/resnet18/CIFAR-10/ReAct/adaptive/std/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -1107,6 +1107,104 @@
       <c r="O15" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=0.5,scale_th=1.0,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>98.27</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>36.51</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>92.98</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>98.03</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>97.09</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>99.44</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>98.05</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>97.31</v>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.3,scale_th=0.5,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>98.26000000000001</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>37.22</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>98.02</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>97.13</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>99.58</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>98.06</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>97.31</v>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.5,scale_th=0.5,type=std</t>
         </is>
       </c>
     </row>
